--- a/ci-cd-merge-resolver/repoCollector/datasets/skywalking.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/skywalking.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -51,6 +51,42 @@
   </si>
   <si>
     <t>bf9887b06b9cac5d0f3528ca370d2527d6add3e1</t>
+  </si>
+  <si>
+    <t>2f02f74dad4b775cd73d2cb1882a9405ef88ef7e</t>
+  </si>
+  <si>
+    <t>192e8a29dd437881f4ec05e747fa3bb9caf7d970</t>
+  </si>
+  <si>
+    <t>e3df9ac2a7f1cecf68b95327dc8f076cdcdba9f3</t>
+  </si>
+  <si>
+    <t>43ca1a0ee79364dca3bf5cde35abb3c8ba5a612a</t>
+  </si>
+  <si>
+    <t>9f373fc2f6086b14a903c45fc96a38f05d87abfa</t>
+  </si>
+  <si>
+    <t>69843b77153c5754972830e47807ae570ff19305</t>
+  </si>
+  <si>
+    <t>014995544463f71c59cab887fb88405ba40ae8b9</t>
+  </si>
+  <si>
+    <t>c83792cd0398169ec9d29455b97f934561b22a06</t>
+  </si>
+  <si>
+    <t>aae50a3480b82f10108432a8f20d6259282c2fc0</t>
+  </si>
+  <si>
+    <t>5b451c8d1b8128de4264a40f95a3c1615afb2228</t>
+  </si>
+  <si>
+    <t>b6d262c2faeaa73eb4a1f7c15b337a28eb815295</t>
+  </si>
+  <si>
+    <t>c5bf7b810e067e2b180b216750b03dae3540da58</t>
   </si>
 </sst>
 </file>
@@ -95,7 +131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -156,10 +192,138 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>1.25</v>
+        <v>0.26899999380111694</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>0.30000001192092896</v>
+      </c>
+      <c r="J3" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>0.3319999873638153</v>
+      </c>
+      <c r="J4" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G5" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>32.90299987792969</v>
+      </c>
+      <c r="J5" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G6" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>33.507999420166016</v>
+      </c>
+      <c r="J6" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ci-cd-merge-resolver/repoCollector/datasets/skywalking.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/skywalking.xlsx
@@ -14,34 +14,34 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
-    <t>mergeCommit</t>
-  </si>
-  <si>
-    <t>parent1</t>
-  </si>
-  <si>
-    <t>parent2</t>
-  </si>
-  <si>
-    <t>numTests</t>
-  </si>
-  <si>
-    <t>numConflictingFiles</t>
-  </si>
-  <si>
-    <t>numJavaFiles</t>
-  </si>
-  <si>
-    <t>compilationSuccess</t>
-  </si>
-  <si>
-    <t>testSuccess</t>
-  </si>
-  <si>
-    <t>elapsedTestTime</t>
-  </si>
-  <si>
-    <t>isMultiModule</t>
+    <t>Merge Commit</t>
+  </si>
+  <si>
+    <t>Parent1</t>
+  </si>
+  <si>
+    <t>Parent2</t>
+  </si>
+  <si>
+    <t>Number of Tests</t>
+  </si>
+  <si>
+    <t>Number of Conflicting Files</t>
+  </si>
+  <si>
+    <t>Number of Java Files</t>
+  </si>
+  <si>
+    <t>Compilation Success</t>
+  </si>
+  <si>
+    <t>Test Success</t>
+  </si>
+  <si>
+    <t>Elapsed Time</t>
+  </si>
+  <si>
+    <t>Multi Module</t>
   </si>
   <si>
     <t>7a91ef7a0255e0da82d300c1b4fbc9b4ea4425ba</t>
@@ -192,10 +192,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.26899999380111694</v>
+        <v>0.6269999742507935</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -224,10 +224,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>0.30000001192092896</v>
+        <v>1.1519999504089355</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -256,10 +256,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>0.3319999873638153</v>
+        <v>1.180999994277954</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -288,10 +288,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>32.90299987792969</v>
+        <v>33.79800033569336</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -320,10 +320,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>33.507999420166016</v>
+        <v>34.05599594116211</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/ci-cd-merge-resolver/repoCollector/datasets/skywalking.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/skywalking.xlsx
@@ -192,7 +192,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.6269999742507935</v>
+        <v>0.6480000019073486</v>
       </c>
       <c r="J2" t="b" s="0">
         <v>1</v>
@@ -224,7 +224,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>1.1519999504089355</v>
+        <v>1.2680000066757202</v>
       </c>
       <c r="J3" t="b" s="0">
         <v>1</v>
@@ -256,7 +256,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>1.180999994277954</v>
+        <v>0.8040000200271606</v>
       </c>
       <c r="J4" t="b" s="0">
         <v>1</v>
@@ -288,7 +288,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>33.79800033569336</v>
+        <v>33.23699951171875</v>
       </c>
       <c r="J5" t="b" s="0">
         <v>1</v>
@@ -320,7 +320,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>34.05599594116211</v>
+        <v>33.65899658203125</v>
       </c>
       <c r="J6" t="b" s="0">
         <v>1</v>

--- a/ci-cd-merge-resolver/repoCollector/datasets/skywalking.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/skywalking.xlsx
@@ -192,7 +192,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.6480000019073486</v>
+        <v>0.7549999952316284</v>
       </c>
       <c r="J2" t="b" s="0">
         <v>1</v>
@@ -224,7 +224,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>1.2680000066757202</v>
+        <v>1.340000033378601</v>
       </c>
       <c r="J3" t="b" s="0">
         <v>1</v>
@@ -256,7 +256,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>0.8040000200271606</v>
+        <v>0.5519999861717224</v>
       </c>
       <c r="J4" t="b" s="0">
         <v>1</v>
@@ -288,7 +288,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>33.23699951171875</v>
+        <v>37.722999572753906</v>
       </c>
       <c r="J5" t="b" s="0">
         <v>1</v>
@@ -320,7 +320,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>33.65899658203125</v>
+        <v>38.05099868774414</v>
       </c>
       <c r="J6" t="b" s="0">
         <v>1</v>

--- a/ci-cd-merge-resolver/repoCollector/datasets/skywalking.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/skywalking.xlsx
@@ -192,7 +192,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.7549999952316284</v>
+        <v>0.5270000100135803</v>
       </c>
       <c r="J2" t="b" s="0">
         <v>1</v>
@@ -224,7 +224,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>1.340000033378601</v>
+        <v>1.3170000314712524</v>
       </c>
       <c r="J3" t="b" s="0">
         <v>1</v>
@@ -256,7 +256,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>0.5519999861717224</v>
+        <v>1.4170000553131104</v>
       </c>
       <c r="J4" t="b" s="0">
         <v>1</v>
@@ -288,7 +288,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>37.722999572753906</v>
+        <v>33.53799819946289</v>
       </c>
       <c r="J5" t="b" s="0">
         <v>1</v>
@@ -320,7 +320,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>38.05099868774414</v>
+        <v>34.26899719238281</v>
       </c>
       <c r="J6" t="b" s="0">
         <v>1</v>

--- a/ci-cd-merge-resolver/repoCollector/datasets/skywalking.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/skywalking.xlsx
@@ -192,7 +192,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.5270000100135803</v>
+        <v>0.609000027179718</v>
       </c>
       <c r="J2" t="b" s="0">
         <v>1</v>
@@ -224,7 +224,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>1.3170000314712524</v>
+        <v>1.2380000352859497</v>
       </c>
       <c r="J3" t="b" s="0">
         <v>1</v>
@@ -256,7 +256,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>1.4170000553131104</v>
+        <v>0.7350000143051147</v>
       </c>
       <c r="J4" t="b" s="0">
         <v>1</v>
@@ -288,7 +288,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>33.53799819946289</v>
+        <v>32.37399673461914</v>
       </c>
       <c r="J5" t="b" s="0">
         <v>1</v>
@@ -320,7 +320,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>34.26899719238281</v>
+        <v>33.12099838256836</v>
       </c>
       <c r="J6" t="b" s="0">
         <v>1</v>
